--- a/src-tauri/help-econometrica/template_retail_ecom.xlsx
+++ b/src-tauri/help-econometrica/template_retail_ecom.xlsx
@@ -171,6 +171,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Aurora AI Econometrica</author>
+    <author>Aurora</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -193,7 +194,7 @@
         <t>[Медиа] Цифра: расход в ₽.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="1" shapeId="0">
       <text>
         <t>[Медиа] Наружка: контакты OTS (физ.).</t>
       </text>
@@ -554,7 +555,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>ooh_ots</t>
+          <t>ooh_contacts</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">

--- a/src-tauri/help-econometrica/template_retail_ecom.xlsx
+++ b/src-tauri/help-econometrica/template_retail_ecom.xlsx
@@ -1,65 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Данные" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>sales_rub</t>
+  </si>
+  <si>
+    <t>tv_spend</t>
+  </si>
+  <si>
+    <t>tv_trp</t>
+  </si>
+  <si>
+    <t>digital_spend</t>
+  </si>
+  <si>
+    <t>digital_impressions</t>
+  </si>
+  <si>
+    <t>ooh_spend</t>
+  </si>
+  <si>
+    <t>ooh_contacts</t>
+  </si>
+  <si>
+    <t>retail_media_spend</t>
+  </si>
+  <si>
+    <t>retail_media_impressions</t>
+  </si>
+  <si>
+    <t>promo_indicator</t>
+  </si>
+  <si>
+    <t>competitor_promo</t>
+  </si>
+  <si>
+    <t>holiday_blackfriday</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9ECFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9F5E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECECEC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -74,158 +88,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Aurora AI Econometrica</author>
-    <author>Aurora</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>[Дата] Период. ГГГГ-ММ-ДД.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>[KPI] Продажи/выручка в ₽ (денежный KPI). Альтернатива — traffic_visits (количественный).</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>[Медиа] ТВ: расход в ₽.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>[Медиа] Цифра: расход в ₽.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="1" shapeId="0">
-      <text>
-        <t>[Медиа] Наружка: контакты OTS (физ.).</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>[Медиа] Retail media (Ozon/WB реклама): расход в ₽.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>[Управляемый] Промо-период (0/1; глубина скидки % точнее, если есть). Наш фактор.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>[Внешний] Промо конкурента (0/1 или индекс). Контроль.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>[Внешний] Чёрная пятница / распродажи (0/1). Контроль.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>[Внешний] Новогодний период (0/1). Контроль.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -512,80 +383,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>sales_rub</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>tv_spend</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>digital_spend</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>ooh_contacts</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>retail_media_spend</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>promo_indicator</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>competitor_promo</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>holiday_blackfriday</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>holiday_newyear</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>